--- a/UnityTableTool/Data/ValidationExamples/02_VALID_SINGLETON.xlsx
+++ b/UnityTableTool/Data/ValidationExamples/02_VALID_SINGLETON.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\ValidationExamples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\Data\ValidationExamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25320" windowHeight="17175"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="VALID_SINGLETON" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>table: VALID_SINGLETON|type:single</t>
   </si>
@@ -40,9 +40,27 @@
     <t/>
   </si>
   <si>
+    <t>id列</t>
+  </si>
+  <si>
+    <t>字段类型</t>
+  </si>
+  <si>
+    <t>字段值</t>
+  </si>
+  <si>
     <t>说明</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>cs</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -52,22 +70,22 @@
     <t>data</t>
   </si>
   <si>
-    <t>cs</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>mode</t>
+    <t>values</t>
+  </si>
+  <si>
+    <t>int()</t>
+  </si>
+  <si>
+    <t>1#2#3</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>说说明</t>
+  </si>
+  <si>
+    <t>slot_num</t>
   </si>
   <si>
     <t>enum(enum1|enum2)</t>
@@ -76,16 +94,19 @@
     <t>enum2</t>
   </si>
   <si>
-    <t>values</t>
-  </si>
-  <si>
-    <t>int()</t>
-  </si>
-  <si>
-    <t>1#2#3</t>
-  </si>
-  <si>
-    <t>说说明</t>
+    <t>team_num</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>预设阵容数量</t>
+  </si>
+  <si>
+    <t>slot_num1</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -98,7 +119,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -119,6 +140,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF374151"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -127,6 +154,11 @@
       <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -595,31 +627,22 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -628,123 +651,132 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -752,10 +784,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1229,14 +1270,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="5" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="25.8181818181818" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="7" max="7" width="7.90909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1252,107 +1296,137 @@
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="2"/>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:6">
+      <c r="B7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>17</v>
+      <c r="E9" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
